--- a/data/trans_orig/Q4506_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49487</t>
+          <t>48660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82395</t>
+          <t>82441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111557</t>
+          <t>111591</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153427</t>
+          <t>152425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170810</t>
+          <t>170083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224007</t>
+          <t>224051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61295</t>
+          <t>60609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93938</t>
+          <t>94389</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78544</t>
+          <t>77948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>115888</t>
+          <t>115705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146908</t>
+          <t>147094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199197</t>
+          <t>195555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74130</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113904</t>
+          <t>112626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113905</t>
+          <t>113317</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154691</t>
+          <t>155369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>195993</t>
+          <t>199696</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>253230</t>
+          <t>256527</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58847</t>
+          <t>58733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90493</t>
+          <t>93217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34031</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58388</t>
+          <t>60176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99171</t>
+          <t>99406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140341</t>
+          <t>141466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368663</t>
+          <t>367856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419904</t>
+          <t>421271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>261417</t>
+          <t>262439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313045</t>
+          <t>319785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>645979</t>
+          <t>644611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>723082</t>
+          <t>722869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>62718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97954</t>
+          <t>96345</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167398</t>
+          <t>165854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221239</t>
+          <t>218931</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>239746</t>
+          <t>243161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304255</t>
+          <t>304220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>65542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100516</t>
+          <t>101801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127298</t>
+          <t>127760</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>172154</t>
+          <t>175780</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>202661</t>
+          <t>201230</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262257</t>
+          <t>263044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120796</t>
+          <t>118688</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>166253</t>
+          <t>165155</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>176277</t>
+          <t>177114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>228668</t>
+          <t>230373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>308798</t>
+          <t>310896</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>379990</t>
+          <t>374739</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111485</t>
+          <t>110090</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>157013</t>
+          <t>156791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75822</t>
+          <t>73694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113586</t>
+          <t>114526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200648</t>
+          <t>198291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254358</t>
+          <t>257209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>546459</t>
+          <t>547881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613271</t>
+          <t>611242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358859</t>
+          <t>361323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>421810</t>
+          <t>425964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>922480</t>
+          <t>922252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1017414</t>
+          <t>1015299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,7%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33268</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62396</t>
+          <t>64644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126623</t>
+          <t>128692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174013</t>
+          <t>176365</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>170085</t>
+          <t>169157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228365</t>
+          <t>224904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53500</t>
+          <t>51881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86929</t>
+          <t>87340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75421</t>
+          <t>74958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113538</t>
+          <t>111119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136916</t>
+          <t>134112</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185999</t>
+          <t>185895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91714</t>
+          <t>93658</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134145</t>
+          <t>135815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117030</t>
+          <t>114869</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160387</t>
+          <t>160464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>221386</t>
+          <t>220729</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>280366</t>
+          <t>280945</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72591</t>
+          <t>72960</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109796</t>
+          <t>107959</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>52100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87133</t>
+          <t>85595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136044</t>
+          <t>136814</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>187380</t>
+          <t>184646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>408256</t>
+          <t>411720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>467459</t>
+          <t>467678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>299754</t>
+          <t>298706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358741</t>
+          <t>357825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>726734</t>
+          <t>727286</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>806775</t>
+          <t>814900</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62605</t>
+          <t>62053</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96518</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207004</t>
+          <t>204064</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>261213</t>
+          <t>261593</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>278103</t>
+          <t>276119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342274</t>
+          <t>342072</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>77468</t>
+          <t>74506</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114154</t>
+          <t>112496</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>161048</t>
+          <t>159493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>211064</t>
+          <t>208443</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246157</t>
+          <t>244126</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>306304</t>
+          <t>312372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>144619</t>
+          <t>147067</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>191390</t>
+          <t>192952</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>160991</t>
+          <t>160017</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>209323</t>
+          <t>207836</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>317574</t>
+          <t>319237</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>385512</t>
+          <t>390186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>122148</t>
+          <t>120827</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>165236</t>
+          <t>166459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82417</t>
+          <t>82889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>121580</t>
+          <t>123388</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>213035</t>
+          <t>212739</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>275262</t>
+          <t>274124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>432649</t>
+          <t>431604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>492736</t>
+          <t>494383</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>319427</t>
+          <t>318555</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>378669</t>
+          <t>384602</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>767457</t>
+          <t>768324</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>861275</t>
+          <t>861346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>237938</t>
+          <t>238341</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>301895</t>
+          <t>299975</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>664050</t>
+          <t>661393</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>763842</t>
+          <t>760420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>911490</t>
+          <t>916521</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1036080</t>
+          <t>1034154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>284114</t>
+          <t>284021</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>355489</t>
+          <t>351772</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>473793</t>
+          <t>478189</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>562163</t>
+          <t>562433</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>781497</t>
+          <t>785808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>896064</t>
+          <t>900498</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>478571</t>
+          <t>470397</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>560521</t>
+          <t>561053</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>606279</t>
+          <t>612613</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>706445</t>
+          <t>704010</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1109561</t>
+          <t>1108717</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1232492</t>
+          <t>1243764</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>399099</t>
+          <t>402097</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>479721</t>
+          <t>481800</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>274124</t>
+          <t>272407</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>345549</t>
+          <t>343370</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>697688</t>
+          <t>695039</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>797203</t>
+          <t>805493</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1814187</t>
+          <t>1822258</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1936800</t>
+          <t>1937460</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1301182</t>
+          <t>1297622</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1419311</t>
+          <t>1415904</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3151595</t>
+          <t>3159503</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3320533</t>
+          <t>3326108</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>40975</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69941</t>
+          <t>69204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>84037</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119416</t>
+          <t>120916</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132907</t>
+          <t>132957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178845</t>
+          <t>179503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75209</t>
+          <t>76535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112018</t>
+          <t>114207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,82 +4501,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>155307</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>135313</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>177553</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>23,16%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>20,17%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>249156</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>223355</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>277226</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>16,6%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>155307</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>133319</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>176285</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>19,88%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>26,28%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>249156</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>221807</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>279443</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>16,48%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68662</t>
+          <t>69219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104208</t>
+          <t>103258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90712</t>
+          <t>87629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127863</t>
+          <t>125749</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167874</t>
+          <t>167901</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>218016</t>
+          <t>217906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44779</t>
+          <t>45570</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75269</t>
+          <t>74266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>45760</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73592</t>
+          <t>72421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97281</t>
+          <t>98579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139033</t>
+          <t>139576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357238</t>
+          <t>357401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407264</t>
+          <t>410425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221719</t>
+          <t>223775</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>274383</t>
+          <t>273198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>597274</t>
+          <t>595825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>671306</t>
+          <t>667113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77021</t>
+          <t>77037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118436</t>
+          <t>115249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158829</t>
+          <t>158149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208528</t>
+          <t>208077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>248330</t>
+          <t>248222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314196</t>
+          <t>311662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169384</t>
+          <t>167393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>221253</t>
+          <t>218494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>223936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>278417</t>
+          <t>281322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>410209</t>
+          <t>409930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>486278</t>
+          <t>484564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128063</t>
+          <t>128901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>175660</t>
+          <t>174392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211262</t>
+          <t>209838</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>269668</t>
+          <t>269353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>355192</t>
+          <t>358206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>427455</t>
+          <t>428569</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109592</t>
+          <t>106310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153849</t>
+          <t>150489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68074</t>
+          <t>69118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105552</t>
+          <t>105485</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>189061</t>
+          <t>186709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>244352</t>
+          <t>247554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>410906</t>
+          <t>412202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>472360</t>
+          <t>478688</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>250658</t>
+          <t>247143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>308493</t>
+          <t>305705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>676633</t>
+          <t>674989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764845</t>
+          <t>761797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80436</t>
+          <t>80842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143491</t>
+          <t>141497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189775</t>
+          <t>188776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198863</t>
+          <t>200712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255617</t>
+          <t>255306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175915</t>
+          <t>177036</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>227748</t>
+          <t>226357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>243050</t>
+          <t>244793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>298373</t>
+          <t>297782</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>436006</t>
+          <t>431343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>512942</t>
+          <t>509014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124282</t>
+          <t>126920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170895</t>
+          <t>172404</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,82 +5978,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>138297</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>118184</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>162673</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>20,85%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>283804</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>252934</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>317714</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>16,49%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,68%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>138297</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>118179</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>162465</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>15,15%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>283804</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>252463</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>316647</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>18,5%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>16,46%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82732</t>
+          <t>81911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119724</t>
+          <t>119942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47981</t>
+          <t>47761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77057</t>
+          <t>77692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>137643</t>
+          <t>138460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184904</t>
+          <t>189044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215845</t>
+          <t>216034</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267421</t>
+          <t>269803</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123961</t>
+          <t>124049</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167624</t>
+          <t>168033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356456</t>
+          <t>352086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>428339</t>
+          <t>420745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101468</t>
+          <t>98878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140444</t>
+          <t>140837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259497</t>
+          <t>260184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>319994</t>
+          <t>321816</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>371343</t>
+          <t>372727</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>450461</t>
+          <t>442964</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>136906</t>
+          <t>134167</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>182051</t>
+          <t>180025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>215820</t>
+          <t>212526</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>270484</t>
+          <t>271908</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>363313</t>
+          <t>361057</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>435508</t>
+          <t>437701</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133655</t>
+          <t>130901</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>177762</t>
+          <t>175691</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120186</t>
+          <t>120269</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>162935</t>
+          <t>165973</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>262631</t>
+          <t>263681</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>325508</t>
+          <t>327386</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93162</t>
+          <t>95210</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134509</t>
+          <t>136035</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64088</t>
+          <t>65147</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98833</t>
+          <t>99635</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>168489</t>
+          <t>167275</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>221452</t>
+          <t>220837</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>362276</t>
+          <t>361808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>423387</t>
+          <t>423931</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>258524</t>
+          <t>261383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>321022</t>
+          <t>320934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>639943</t>
+          <t>643545</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>728824</t>
+          <t>725952</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>297102</t>
+          <t>301654</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>370333</t>
+          <t>371322</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>682798</t>
+          <t>689529</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>791879</t>
+          <t>784511</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1006133</t>
+          <t>1005046</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1133260</t>
+          <t>1134760</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>601741</t>
+          <t>602023</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>695710</t>
+          <t>692471</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>869804</t>
+          <t>868070</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>974100</t>
+          <t>977602</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1493335</t>
+          <t>1500954</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1637378</t>
+          <t>1639322</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>491122</t>
+          <t>492040</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>579815</t>
+          <t>579463</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>577867</t>
+          <t>578316</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>668512</t>
+          <t>668315</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1099234</t>
+          <t>1101547</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1221363</t>
+          <t>1222539</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>360855</t>
+          <t>364918</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>436974</t>
+          <t>441971</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>252221</t>
+          <t>254995</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>317800</t>
+          <t>323173</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>635888</t>
+          <t>637369</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>739363</t>
+          <t>737097</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1397019</t>
+          <t>1399609</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1519989</t>
+          <t>1511904</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>908037</t>
+          <t>908927</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1016855</t>
+          <t>1016924</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2343967</t>
+          <t>2344262</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2506472</t>
+          <t>2502378</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4506_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48660</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82441</t>
+          <t>82765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111591</t>
+          <t>113101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152425</t>
+          <t>155772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170083</t>
+          <t>170701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224051</t>
+          <t>222937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60609</t>
+          <t>60856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94389</t>
+          <t>95342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77948</t>
+          <t>77115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>115705</t>
+          <t>116647</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147094</t>
+          <t>147621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195555</t>
+          <t>200776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75672</t>
+          <t>76242</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112626</t>
+          <t>113947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113317</t>
+          <t>113866</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>155369</t>
+          <t>157094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>199696</t>
+          <t>197597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256527</t>
+          <t>254104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58733</t>
+          <t>57532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93217</t>
+          <t>91472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>33723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60176</t>
+          <t>59739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99406</t>
+          <t>101093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141466</t>
+          <t>142653</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367856</t>
+          <t>369391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421271</t>
+          <t>420546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262439</t>
+          <t>261300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>319785</t>
+          <t>313262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>644611</t>
+          <t>643627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722869</t>
+          <t>723664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62718</t>
+          <t>62644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96345</t>
+          <t>96788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165854</t>
+          <t>169293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>218931</t>
+          <t>217988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243161</t>
+          <t>243257</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304220</t>
+          <t>303830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65542</t>
+          <t>65514</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101801</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127760</t>
+          <t>126668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175780</t>
+          <t>175018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201230</t>
+          <t>199483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>263044</t>
+          <t>258768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118688</t>
+          <t>121003</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>165155</t>
+          <t>167874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>177114</t>
+          <t>177331</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>230373</t>
+          <t>226260</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>310896</t>
+          <t>312527</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374739</t>
+          <t>378342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110090</t>
+          <t>112371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156791</t>
+          <t>157588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73694</t>
+          <t>77022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114526</t>
+          <t>113344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198291</t>
+          <t>200264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257209</t>
+          <t>256984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547881</t>
+          <t>543840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>611242</t>
+          <t>613449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361323</t>
+          <t>357634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>425964</t>
+          <t>423079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>922252</t>
+          <t>921861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1015299</t>
+          <t>1013321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64644</t>
+          <t>64414</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>128692</t>
+          <t>128255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176365</t>
+          <t>175780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>169157</t>
+          <t>169395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>224904</t>
+          <t>227529</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51881</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87340</t>
+          <t>86078</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74958</t>
+          <t>72695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111119</t>
+          <t>110719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134112</t>
+          <t>133862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185895</t>
+          <t>184649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93658</t>
+          <t>92493</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135815</t>
+          <t>134861</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114869</t>
+          <t>118440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160464</t>
+          <t>163746</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>220729</t>
+          <t>220632</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>280945</t>
+          <t>278731</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72960</t>
+          <t>74527</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107959</t>
+          <t>113018</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52100</t>
+          <t>52858</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85595</t>
+          <t>87170</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136814</t>
+          <t>136756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184646</t>
+          <t>186555</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>411720</t>
+          <t>410548</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>467678</t>
+          <t>470488</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>298706</t>
+          <t>301460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>357825</t>
+          <t>358115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>727286</t>
+          <t>729741</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>814900</t>
+          <t>812013</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62053</t>
+          <t>61969</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96546</t>
+          <t>99183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>204064</t>
+          <t>206085</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>261593</t>
+          <t>260059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276119</t>
+          <t>275992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342072</t>
+          <t>341800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74506</t>
+          <t>74528</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112496</t>
+          <t>113016</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>159493</t>
+          <t>161085</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208443</t>
+          <t>209462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244126</t>
+          <t>247588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>312372</t>
+          <t>310776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>147067</t>
+          <t>146138</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192952</t>
+          <t>193198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>160017</t>
+          <t>158268</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>207836</t>
+          <t>208854</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>319237</t>
+          <t>318734</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>390186</t>
+          <t>386031</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120827</t>
+          <t>121225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>166459</t>
+          <t>166277</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82889</t>
+          <t>80526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123388</t>
+          <t>119830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>212739</t>
+          <t>214624</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274124</t>
+          <t>275080</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>431604</t>
+          <t>430277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>494383</t>
+          <t>496038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>318555</t>
+          <t>321284</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>384602</t>
+          <t>383322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>768324</t>
+          <t>773296</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>861346</t>
+          <t>862921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,24%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238341</t>
+          <t>237615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>299975</t>
+          <t>301341</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>661393</t>
+          <t>660646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>760420</t>
+          <t>762143</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>916521</t>
+          <t>916001</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1034154</t>
+          <t>1042034</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>284021</t>
+          <t>284772</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>351772</t>
+          <t>354953</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>478189</t>
+          <t>477316</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>562433</t>
+          <t>565190</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>785808</t>
+          <t>772834</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>900498</t>
+          <t>893190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>470397</t>
+          <t>474972</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561053</t>
+          <t>560350</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>612613</t>
+          <t>610985</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>704010</t>
+          <t>706379</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1108717</t>
+          <t>1108671</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1243764</t>
+          <t>1242232</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>402097</t>
+          <t>399369</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>481800</t>
+          <t>481606</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>272407</t>
+          <t>271802</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>343370</t>
+          <t>340699</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>695039</t>
+          <t>697794</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>805493</t>
+          <t>803616</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1822258</t>
+          <t>1814879</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1937460</t>
+          <t>1941264</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1297622</t>
+          <t>1301373</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1415904</t>
+          <t>1419168</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3159503</t>
+          <t>3154236</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3326108</t>
+          <t>3330002</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40975</t>
+          <t>40733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69204</t>
+          <t>68655</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84037</t>
+          <t>83877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120916</t>
+          <t>120181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>132957</t>
+          <t>132166</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>179503</t>
+          <t>180339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76535</t>
+          <t>76686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114207</t>
+          <t>113460</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135313</t>
+          <t>134116</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>177553</t>
+          <t>177388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>223355</t>
+          <t>221589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277226</t>
+          <t>277853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69219</t>
+          <t>68415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103258</t>
+          <t>102903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87629</t>
+          <t>89105</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125749</t>
+          <t>125727</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167901</t>
+          <t>168178</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>217906</t>
+          <t>219280</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45570</t>
+          <t>45358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74266</t>
+          <t>75981</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45760</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72421</t>
+          <t>72912</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98579</t>
+          <t>97642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139576</t>
+          <t>139784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357401</t>
+          <t>355460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410425</t>
+          <t>411129</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>223775</t>
+          <t>226783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>273198</t>
+          <t>274742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>595825</t>
+          <t>596309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>667113</t>
+          <t>668442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77037</t>
+          <t>78631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115249</t>
+          <t>116232</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158149</t>
+          <t>159971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208077</t>
+          <t>211275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>248222</t>
+          <t>247788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311662</t>
+          <t>311904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167393</t>
+          <t>168640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218494</t>
+          <t>218765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223936</t>
+          <t>226583</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>281322</t>
+          <t>279762</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>409930</t>
+          <t>410425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>484564</t>
+          <t>485923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128901</t>
+          <t>127769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>174392</t>
+          <t>175091</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>209838</t>
+          <t>211813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>269353</t>
+          <t>267924</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>358206</t>
+          <t>355415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>428569</t>
+          <t>426795</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106310</t>
+          <t>110101</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150489</t>
+          <t>153264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69118</t>
+          <t>67572</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105485</t>
+          <t>103869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186709</t>
+          <t>186792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247554</t>
+          <t>247664</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>412202</t>
+          <t>411495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>478688</t>
+          <t>471734</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247143</t>
+          <t>248191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>305705</t>
+          <t>306283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674989</t>
+          <t>678975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761797</t>
+          <t>763256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49198</t>
+          <t>49405</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80842</t>
+          <t>82513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141497</t>
+          <t>138757</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188776</t>
+          <t>187530</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200712</t>
+          <t>201886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255306</t>
+          <t>260503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177036</t>
+          <t>178423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>226357</t>
+          <t>228334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>244793</t>
+          <t>241546</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>297782</t>
+          <t>297936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>431343</t>
+          <t>436464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>509014</t>
+          <t>511175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126920</t>
+          <t>121651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172404</t>
+          <t>167884</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118184</t>
+          <t>117410</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162673</t>
+          <t>160264</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>252934</t>
+          <t>252044</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>317714</t>
+          <t>314689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81911</t>
+          <t>82133</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>121194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47761</t>
+          <t>48329</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77692</t>
+          <t>78157</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138460</t>
+          <t>137140</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189044</t>
+          <t>186226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216034</t>
+          <t>216820</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269803</t>
+          <t>269238</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>124049</t>
+          <t>124854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>168033</t>
+          <t>169566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>352086</t>
+          <t>355006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420745</t>
+          <t>425944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98878</t>
+          <t>100832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140837</t>
+          <t>142953</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>260184</t>
+          <t>259241</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>321816</t>
+          <t>317210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>372727</t>
+          <t>373105</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>442964</t>
+          <t>449893</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134167</t>
+          <t>136233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>180025</t>
+          <t>181883</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>212526</t>
+          <t>214032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>271908</t>
+          <t>270929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>361057</t>
+          <t>361673</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437701</t>
+          <t>436389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>130901</t>
+          <t>129975</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>175691</t>
+          <t>174856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>120269</t>
+          <t>120509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>165973</t>
+          <t>164610</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>263681</t>
+          <t>263990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327386</t>
+          <t>326482</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>93687</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136035</t>
+          <t>131165</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65147</t>
+          <t>62929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>99635</t>
+          <t>97526</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167275</t>
+          <t>167452</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220837</t>
+          <t>223339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>361808</t>
+          <t>360285</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>423931</t>
+          <t>420725</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>261383</t>
+          <t>262290</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>320934</t>
+          <t>320860</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>643545</t>
+          <t>639590</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>725952</t>
+          <t>729551</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>301654</t>
+          <t>302487</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>371322</t>
+          <t>372784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>689529</t>
+          <t>692019</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>784511</t>
+          <t>792978</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1005046</t>
+          <t>1008203</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1134760</t>
+          <t>1134726</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>602023</t>
+          <t>603562</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>692471</t>
+          <t>694636</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>868070</t>
+          <t>867576</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>977602</t>
+          <t>976943</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1500954</t>
+          <t>1496288</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1639322</t>
+          <t>1647704</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>492040</t>
+          <t>487993</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>579463</t>
+          <t>576780</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>578316</t>
+          <t>580591</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>668315</t>
+          <t>670217</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1101547</t>
+          <t>1095896</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1222539</t>
+          <t>1223810</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>364918</t>
+          <t>361922</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>441971</t>
+          <t>438995</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>254995</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>323173</t>
+          <t>321140</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>637369</t>
+          <t>640149</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>737097</t>
+          <t>739219</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1399609</t>
+          <t>1404912</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1511904</t>
+          <t>1517238</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>908927</t>
+          <t>909067</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1016924</t>
+          <t>1019554</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2344262</t>
+          <t>2338813</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2502378</t>
+          <t>2499960</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
